--- a/Luban/DataTables/Datas/HomeTab.xlsx
+++ b/Luban/DataTables/Datas/HomeTab.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26640" windowHeight="8700"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -38,10 +38,10 @@
     <t>##value</t>
   </si>
   <si>
-    <t>atlas</t>
-  </si>
-  <si>
-    <t>sprite</t>
+    <t>iconIds</t>
+  </si>
+  <si>
+    <t>name</t>
   </si>
   <si>
     <t>##type</t>
@@ -53,6 +53,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=;),(int#ref=demo.IconRecord)</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -71,31 +74,34 @@
     <t>图标</t>
   </si>
   <si>
-    <t>HomeTabBar</t>
-  </si>
-  <si>
-    <t>shop0</t>
-  </si>
-  <si>
-    <t>shop1</t>
-  </si>
-  <si>
-    <t>setting0</t>
-  </si>
-  <si>
-    <t>setting1</t>
-  </si>
-  <si>
-    <t>game0</t>
-  </si>
-  <si>
-    <t>game1</t>
-  </si>
-  <si>
-    <t>player0</t>
-  </si>
-  <si>
-    <t>player1</t>
+    <t>1001;1002</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>1003;1004</t>
+  </si>
+  <si>
+    <t>英雄</t>
+  </si>
+  <si>
+    <t>1005;1006</t>
+  </si>
+  <si>
+    <t>游戏</t>
+  </si>
+  <si>
+    <t>1007;1008</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>1009;1010</t>
+  </si>
+  <si>
+    <t>设置</t>
   </si>
 </sst>
 </file>
@@ -711,11 +717,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1037,7 +1046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="20.375" style="1" customWidth="1"/>
@@ -1075,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
@@ -1083,126 +1092,91 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="1">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="1">
-        <v>1003</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="1">
-        <v>1004</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="1">
-        <v>1005</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="1">
-        <v>1006</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="1">
-        <v>1007</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="1">
-        <v>1008</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/HomeTab.xlsx
+++ b/Luban/DataTables/Datas/HomeTab.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowWidth="26880" windowHeight="9285"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -56,6 +56,9 @@
     <t>(list#sep=;),(int#ref=demo.IconRecord)</t>
   </si>
   <si>
+    <t>int#ref=demo.DictionaryRecord</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -77,31 +80,16 @@
     <t>1001;1002</t>
   </si>
   <si>
-    <t>商店</t>
-  </si>
-  <si>
     <t>1003;1004</t>
   </si>
   <si>
-    <t>英雄</t>
-  </si>
-  <si>
     <t>1005;1006</t>
   </si>
   <si>
-    <t>游戏</t>
-  </si>
-  <si>
     <t>1007;1008</t>
   </si>
   <si>
-    <t>事件</t>
-  </si>
-  <si>
     <t>1009;1010</t>
-  </si>
-  <si>
-    <t>设置</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1040,7 @@
     <col min="2" max="2" width="20.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="32.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33" style="1" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1087,41 +1075,41 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -1129,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="E5" s="1">
+        <v>100101</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -1142,8 +1130,8 @@
       <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
+      <c r="E6" s="1">
+        <v>100102</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -1151,10 +1139,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100103</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -1162,10 +1150,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100104</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -1173,10 +1161,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100105</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/HomeTab.xlsx
+++ b/Luban/DataTables/Datas/HomeTab.xlsx
@@ -53,10 +53,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=;),(int#ref=demo.IconRecord)</t>
-  </si>
-  <si>
-    <t>int#ref=demo.DictionaryRecord</t>
+    <t>(list#sep=;),(int#ref=Res.IconRecord)</t>
+  </si>
+  <si>
+    <t>int#ref=Common.TextRecord</t>
   </si>
   <si>
     <t>##group</t>
@@ -74,22 +74,22 @@
     <t>图集</t>
   </si>
   <si>
-    <t>图标</t>
-  </si>
-  <si>
-    <t>1001;1002</t>
-  </si>
-  <si>
-    <t>1003;1004</t>
-  </si>
-  <si>
-    <t>1005;1006</t>
-  </si>
-  <si>
-    <t>1007;1008</t>
-  </si>
-  <si>
-    <t>1009;1010</t>
+    <t>字典</t>
+  </si>
+  <si>
+    <t>100001;100002</t>
+  </si>
+  <si>
+    <t>100003;100004</t>
+  </si>
+  <si>
+    <t>100005;100006</t>
+  </si>
+  <si>
+    <t>100007;100008</t>
+  </si>
+  <si>
+    <t>100009;100010</t>
   </si>
 </sst>
 </file>

--- a/Luban/DataTables/Datas/HomeTab.xlsx
+++ b/Luban/DataTables/Datas/HomeTab.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,10 +53,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=;),(int#ref=Res.IconRecord)</t>
-  </si>
-  <si>
-    <t>int#ref=Common.TextRecord</t>
+    <t>(list#sep=;),(int#ref=Res.Icon)</t>
+  </si>
+  <si>
+    <t>int#ref=Common.Dictionary</t>
   </si>
   <si>
     <t>##group</t>
